--- a/data/Starting/ADRECES_FINAL_15_09_026.xlsx
+++ b/data/Starting/ADRECES_FINAL_15_09_026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lgonzale\Desktop\ATDOM_SCRIPTS\proyecto_atdom\data\Starting\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usr\Desktop\ATDOM_GIT\proyecto_atdom\data\Starting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FB645F-4D0A-471D-944A-495C2B777366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D7F7E9A-A5B9-4AFF-AFA1-FEA0782AB7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17898" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17935" uniqueCount="594">
   <si>
     <t>USUA_SITUACIO</t>
   </si>
@@ -1826,8 +1826,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss\ \U\T\C"/>
-    <numFmt numFmtId="166" formatCode="0000"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="0000"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -1872,11 +1872,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2182,7 +2182,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N2577"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" customWidth="1"/>
     <col min="2" max="2" width="20.140625" customWidth="1"/>
@@ -4130,8 +4130,8 @@
       <c r="K60" t="s">
         <v>16</v>
       </c>
-      <c r="M60" t="e">
-        <v>#N/A</v>
+      <c r="M60" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
@@ -7414,8 +7414,8 @@
       <c r="K163" t="s">
         <v>16</v>
       </c>
-      <c r="M163" t="e">
-        <v>#N/A</v>
+      <c r="M163" t="s">
+        <v>590</v>
       </c>
       <c r="N163" s="2">
         <v>45741.916666666672</v>
@@ -9157,8 +9157,8 @@
       <c r="K217" t="s">
         <v>16</v>
       </c>
-      <c r="M217" t="e">
-        <v>#N/A</v>
+      <c r="M217" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.25">
@@ -11819,8 +11819,8 @@
       <c r="K300" t="s">
         <v>16</v>
       </c>
-      <c r="M300" t="e">
-        <v>#N/A</v>
+      <c r="M300" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.25">
@@ -14313,8 +14313,8 @@
       <c r="K377" t="s">
         <v>16</v>
       </c>
-      <c r="M377" t="e">
-        <v>#N/A</v>
+      <c r="M377" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="378" spans="1:14" x14ac:dyDescent="0.25">
@@ -14816,8 +14816,8 @@
       <c r="K393" t="s">
         <v>16</v>
       </c>
-      <c r="M393" t="e">
-        <v>#N/A</v>
+      <c r="M393" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="394" spans="1:14" x14ac:dyDescent="0.25">
@@ -18871,8 +18871,8 @@
       <c r="K520" t="s">
         <v>16</v>
       </c>
-      <c r="M520" t="e">
-        <v>#N/A</v>
+      <c r="M520" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="521" spans="1:14" x14ac:dyDescent="0.25">
@@ -19226,8 +19226,8 @@
       <c r="K531" t="s">
         <v>16</v>
       </c>
-      <c r="M531" t="e">
-        <v>#N/A</v>
+      <c r="M531" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="532" spans="1:14" x14ac:dyDescent="0.25">
@@ -19418,8 +19418,8 @@
       <c r="K537" t="s">
         <v>16</v>
       </c>
-      <c r="M537" t="e">
-        <v>#N/A</v>
+      <c r="M537" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="538" spans="1:14" x14ac:dyDescent="0.25">
@@ -19712,8 +19712,8 @@
       <c r="K546" t="s">
         <v>16</v>
       </c>
-      <c r="M546" t="e">
-        <v>#N/A</v>
+      <c r="M546" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="547" spans="1:13" x14ac:dyDescent="0.25">
@@ -20343,8 +20343,8 @@
       <c r="K566" t="s">
         <v>16</v>
       </c>
-      <c r="M566" t="e">
-        <v>#N/A</v>
+      <c r="M566" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="567" spans="1:13" x14ac:dyDescent="0.25">
@@ -23977,8 +23977,8 @@
       <c r="K679" t="s">
         <v>16</v>
       </c>
-      <c r="M679" t="e">
-        <v>#N/A</v>
+      <c r="M679" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="680" spans="1:13" x14ac:dyDescent="0.25">
@@ -25257,8 +25257,8 @@
       <c r="K719" t="s">
         <v>16</v>
       </c>
-      <c r="M719" t="e">
-        <v>#N/A</v>
+      <c r="M719" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="720" spans="1:13" x14ac:dyDescent="0.25">
@@ -29583,8 +29583,8 @@
       <c r="K854" t="s">
         <v>16</v>
       </c>
-      <c r="M854" t="e">
-        <v>#N/A</v>
+      <c r="M854" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="855" spans="1:13" x14ac:dyDescent="0.25">
@@ -36167,8 +36167,8 @@
       <c r="K1059" t="s">
         <v>16</v>
       </c>
-      <c r="M1059" t="e">
-        <v>#N/A</v>
+      <c r="M1059" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="1060" spans="1:14" x14ac:dyDescent="0.25">
@@ -37700,8 +37700,8 @@
       <c r="K1107" t="s">
         <v>16</v>
       </c>
-      <c r="M1107" t="e">
-        <v>#N/A</v>
+      <c r="M1107" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="1108" spans="1:14" x14ac:dyDescent="0.25">
@@ -41258,8 +41258,8 @@
       <c r="K1218" t="s">
         <v>16</v>
       </c>
-      <c r="M1218" t="e">
-        <v>#N/A</v>
+      <c r="M1218" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="1219" spans="1:14" x14ac:dyDescent="0.25">
@@ -50577,8 +50577,8 @@
       <c r="K1508" t="s">
         <v>16</v>
       </c>
-      <c r="M1508" t="e">
-        <v>#N/A</v>
+      <c r="M1508" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="1509" spans="1:14" x14ac:dyDescent="0.25">
@@ -56050,8 +56050,8 @@
       <c r="K1678" t="s">
         <v>16</v>
       </c>
-      <c r="M1678" t="e">
-        <v>#N/A</v>
+      <c r="M1678" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="1679" spans="1:14" x14ac:dyDescent="0.25">
@@ -56242,8 +56242,8 @@
       <c r="K1684" t="s">
         <v>16</v>
       </c>
-      <c r="M1684" t="e">
-        <v>#N/A</v>
+      <c r="M1684" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="1685" spans="1:14" x14ac:dyDescent="0.25">
@@ -57135,8 +57135,8 @@
       <c r="K1712" t="s">
         <v>16</v>
       </c>
-      <c r="M1712" t="e">
-        <v>#N/A</v>
+      <c r="M1712" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="1713" spans="1:13" x14ac:dyDescent="0.25">
@@ -59189,8 +59189,8 @@
       <c r="K1776" t="s">
         <v>16</v>
       </c>
-      <c r="M1776" t="e">
-        <v>#N/A</v>
+      <c r="M1776" t="s">
+        <v>590</v>
       </c>
       <c r="N1776" s="2">
         <v>46189.916666666672</v>
@@ -59614,8 +59614,8 @@
       <c r="K1789" t="s">
         <v>16</v>
       </c>
-      <c r="M1789" t="e">
-        <v>#N/A</v>
+      <c r="M1789" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="1790" spans="1:14" x14ac:dyDescent="0.25">
@@ -61453,8 +61453,8 @@
       <c r="K1846" t="s">
         <v>16</v>
       </c>
-      <c r="M1846" t="e">
-        <v>#N/A</v>
+      <c r="M1846" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="1847" spans="1:14" x14ac:dyDescent="0.25">
@@ -63975,8 +63975,8 @@
       <c r="K1925" t="s">
         <v>16</v>
       </c>
-      <c r="M1925" t="e">
-        <v>#N/A</v>
+      <c r="M1925" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="1926" spans="1:14" x14ac:dyDescent="0.25">
@@ -64993,8 +64993,8 @@
       <c r="K1957" t="s">
         <v>16</v>
       </c>
-      <c r="M1957" t="e">
-        <v>#N/A</v>
+      <c r="M1957" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="1958" spans="1:13" x14ac:dyDescent="0.25">
@@ -66556,8 +66556,8 @@
       <c r="K2005" t="s">
         <v>16</v>
       </c>
-      <c r="M2005" t="e">
-        <v>#N/A</v>
+      <c r="M2005" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="2006" spans="1:14" x14ac:dyDescent="0.25">
@@ -67894,8 +67894,8 @@
       <c r="K2047" t="s">
         <v>16</v>
       </c>
-      <c r="M2047" t="e">
-        <v>#N/A</v>
+      <c r="M2047" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="2048" spans="1:14" x14ac:dyDescent="0.25">
@@ -72598,8 +72598,8 @@
       <c r="K2194" t="s">
         <v>16</v>
       </c>
-      <c r="M2194" t="e">
-        <v>#N/A</v>
+      <c r="M2194" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="2195" spans="1:14" x14ac:dyDescent="0.25">
@@ -73279,8 +73279,8 @@
       <c r="K2215" t="s">
         <v>16</v>
       </c>
-      <c r="M2215" t="e">
-        <v>#N/A</v>
+      <c r="M2215" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="2216" spans="1:14" x14ac:dyDescent="0.25">
@@ -74321,8 +74321,8 @@
       <c r="K2247" t="s">
         <v>16</v>
       </c>
-      <c r="M2247" t="e">
-        <v>#N/A</v>
+      <c r="M2247" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="2248" spans="1:14" x14ac:dyDescent="0.25">
@@ -74874,8 +74874,8 @@
       <c r="K2264" t="s">
         <v>16</v>
       </c>
-      <c r="M2264" t="e">
-        <v>#N/A</v>
+      <c r="M2264" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="2265" spans="1:14" x14ac:dyDescent="0.25">
@@ -75168,8 +75168,8 @@
       <c r="K2273" t="s">
         <v>16</v>
       </c>
-      <c r="M2273" t="e">
-        <v>#N/A</v>
+      <c r="M2273" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="2274" spans="1:13" x14ac:dyDescent="0.25">
@@ -76489,8 +76489,8 @@
       <c r="K2314" t="s">
         <v>16</v>
       </c>
-      <c r="M2314" t="e">
-        <v>#N/A</v>
+      <c r="M2314" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="2315" spans="1:14" x14ac:dyDescent="0.25">
@@ -76556,8 +76556,8 @@
       <c r="K2316" t="s">
         <v>16</v>
       </c>
-      <c r="M2316" t="e">
-        <v>#N/A</v>
+      <c r="M2316" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="2317" spans="1:14" x14ac:dyDescent="0.25">
@@ -79416,8 +79416,8 @@
       <c r="K2405" t="s">
         <v>16</v>
       </c>
-      <c r="M2405" t="e">
-        <v>#N/A</v>
+      <c r="M2405" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="2406" spans="1:13" x14ac:dyDescent="0.25">
@@ -84176,8 +84176,8 @@
       <c r="K2553" t="s">
         <v>16</v>
       </c>
-      <c r="M2553" t="e">
-        <v>#N/A</v>
+      <c r="M2553" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="2554" spans="1:14" x14ac:dyDescent="0.25">
@@ -84949,6 +84949,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N2577" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>